--- a/output/laminas_comunales/comunal_o_ocup_a_2022_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,307 @@
         </is>
       </c>
       <c r="C2">
+        <v>51.3543811484786</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>51.3283225184196</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>51.2997254181133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>47.225776370576</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>47.1890547263682</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>47.1338389263667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>40.4595728076388</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>40.4166584924045</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>40.3538634873014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C11">
         <v>35.4081377504744</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>35.3764713168591</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>35.3301958574958</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>30.3888459896846</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>30.3672399001716</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>30.3344602012218</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>29.2519023153986</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>29.2397468639676</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>29.2030703555738</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>10.9600470467159</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>10.9507549973284</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>10.9323171838142</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_o_ocup_a_2022_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,307 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>51.3543811484786</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>51.3283225184196</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>51.2997254181133</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>47.225776370576</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>47.1890547263682</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>47.1338389263667</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>40.4595728076388</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>40.4166584924045</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>40.3538634873014</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C11">
         <v>35.4081377504744</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>35.3764713168591</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>35.3301958574958</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>30.3888459896846</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>30.3672399001716</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>30.3344602012218</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>29.2519023153986</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>29.2397468639676</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>29.2030703555738</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>10.9600470467159</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>10.9507549973284</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>10.9323171838142</v>
       </c>
     </row>
   </sheetData>
